--- a/待规划小区/cell-tree-export-20250915204721.xlsx
+++ b/待规划小区/cell-tree-export-20250915204721.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="23837" windowHeight="11520" activeTab="1"/>
+    <workbookView windowWidth="24685" windowHeight="11520"/>
   </bookViews>
   <sheets>
     <sheet name="LTE" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="5">
   <si>
     <t>MCC</t>
   </si>
@@ -44,9 +44,6 @@
   <si>
     <t>gNodeBID</t>
   </si>
-  <si>
-    <t>01</t>
-  </si>
 </sst>
 </file>
 
@@ -89,8 +86,10 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -431,27 +430,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="9">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -555,19 +539,19 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -576,7 +560,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -588,34 +572,34 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -707,16 +691,11 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1100,8 +1079,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:D25"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="3"/>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="6" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="2" width="3.8" customWidth="1"/>
     <col min="3" max="3" width="9.4" customWidth="1"/>
@@ -1123,339 +1102,87 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="2">
+      <c r="A2" s="5">
         <v>460</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" s="6">
         <v>11</v>
       </c>
-      <c r="C2" s="6">
-        <v>541215</v>
-      </c>
-      <c r="D2" s="6">
-        <v>20</v>
+      <c r="C2" s="4">
+        <v>999999</v>
+      </c>
+      <c r="D2" s="4">
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="2">
+      <c r="A3" s="5">
         <v>460</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="6">
         <v>11</v>
       </c>
-      <c r="C3" s="6">
-        <v>541215</v>
-      </c>
-      <c r="D3" s="6">
-        <v>21</v>
+      <c r="C3" s="4">
+        <v>999999</v>
+      </c>
+      <c r="D3" s="4">
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="2">
+      <c r="A4" s="5">
         <v>460</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="6">
         <v>11</v>
       </c>
-      <c r="C4" s="6">
-        <v>541215</v>
-      </c>
-      <c r="D4" s="6">
-        <v>19</v>
+      <c r="C4" s="4">
+        <v>999999</v>
+      </c>
+      <c r="D4" s="4">
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="2">
+      <c r="A5" s="5">
         <v>460</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="6">
         <v>11</v>
       </c>
-      <c r="C5" s="6">
-        <v>542588</v>
-      </c>
-      <c r="D5" s="6">
+      <c r="C5" s="4">
+        <v>888888</v>
+      </c>
+      <c r="D5" s="4">
         <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="2">
+      <c r="A6" s="5">
         <v>460</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="6">
         <v>11</v>
       </c>
-      <c r="C6" s="6">
-        <v>542588</v>
-      </c>
-      <c r="D6" s="6">
+      <c r="C6" s="4">
+        <v>888888</v>
+      </c>
+      <c r="D6" s="4">
         <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="2">
+      <c r="A7" s="5">
         <v>460</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="6">
         <v>11</v>
       </c>
-      <c r="C7" s="6">
-        <v>542588</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C7" s="4">
+        <v>888888</v>
+      </c>
+      <c r="D7" s="4">
         <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="2">
-        <v>460</v>
-      </c>
-      <c r="B8" s="3">
-        <v>11</v>
-      </c>
-      <c r="C8" s="6">
-        <v>540698</v>
-      </c>
-      <c r="D8" s="6">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="2">
-        <v>460</v>
-      </c>
-      <c r="B9" s="3">
-        <v>11</v>
-      </c>
-      <c r="C9" s="6">
-        <v>540698</v>
-      </c>
-      <c r="D9" s="6">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="2">
-        <v>460</v>
-      </c>
-      <c r="B10" s="3">
-        <v>11</v>
-      </c>
-      <c r="C10" s="6">
-        <v>540698</v>
-      </c>
-      <c r="D10" s="6">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="2">
-        <v>460</v>
-      </c>
-      <c r="B11" s="3">
-        <v>11</v>
-      </c>
-      <c r="C11" s="6">
-        <v>540845</v>
-      </c>
-      <c r="D11">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="2">
-        <v>460</v>
-      </c>
-      <c r="B12" s="3">
-        <v>11</v>
-      </c>
-      <c r="C12" s="6">
-        <v>540845</v>
-      </c>
-      <c r="D12">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="2">
-        <v>460</v>
-      </c>
-      <c r="B13" s="3">
-        <v>11</v>
-      </c>
-      <c r="C13" s="6">
-        <v>540845</v>
-      </c>
-      <c r="D13">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="2">
-        <v>460</v>
-      </c>
-      <c r="B14" s="3">
-        <v>11</v>
-      </c>
-      <c r="C14" s="6">
-        <v>541227</v>
-      </c>
-      <c r="D14">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="2">
-        <v>460</v>
-      </c>
-      <c r="B15" s="3">
-        <v>11</v>
-      </c>
-      <c r="C15" s="6">
-        <v>541227</v>
-      </c>
-      <c r="D15">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="2">
-        <v>460</v>
-      </c>
-      <c r="B16" s="3">
-        <v>11</v>
-      </c>
-      <c r="C16" s="6">
-        <v>541227</v>
-      </c>
-      <c r="D16">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="2">
-        <v>460</v>
-      </c>
-      <c r="B17" s="3">
-        <v>11</v>
-      </c>
-      <c r="C17" s="6">
-        <v>936201</v>
-      </c>
-      <c r="D17" s="6">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="2">
-        <v>460</v>
-      </c>
-      <c r="B18" s="3">
-        <v>11</v>
-      </c>
-      <c r="C18" s="6">
-        <v>936201</v>
-      </c>
-      <c r="D18" s="6">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="2">
-        <v>460</v>
-      </c>
-      <c r="B19" s="3">
-        <v>11</v>
-      </c>
-      <c r="C19" s="6">
-        <v>936333</v>
-      </c>
-      <c r="D19" s="6">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" s="2">
-        <v>460</v>
-      </c>
-      <c r="B20" s="3">
-        <v>11</v>
-      </c>
-      <c r="C20" s="6">
-        <v>936260</v>
-      </c>
-      <c r="D20" s="6">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" s="2">
-        <v>460</v>
-      </c>
-      <c r="B21" s="3">
-        <v>11</v>
-      </c>
-      <c r="C21" s="6">
-        <v>936201</v>
-      </c>
-      <c r="D21" s="6">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" s="2">
-        <v>460</v>
-      </c>
-      <c r="B22" s="3">
-        <v>11</v>
-      </c>
-      <c r="C22" s="6">
-        <v>542333</v>
-      </c>
-      <c r="D22" s="6">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" s="2">
-        <v>460</v>
-      </c>
-      <c r="B23" s="3">
-        <v>11</v>
-      </c>
-      <c r="C23" s="6">
-        <v>936260</v>
-      </c>
-      <c r="D23" s="6">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24" s="2">
-        <v>460</v>
-      </c>
-      <c r="B24" s="3">
-        <v>11</v>
-      </c>
-      <c r="C24" s="6">
-        <v>936260</v>
-      </c>
-      <c r="D24" s="6">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" s="2">
-        <v>460</v>
-      </c>
-      <c r="B25" s="3">
-        <v>11</v>
-      </c>
-      <c r="C25" s="6">
-        <v>936260</v>
-      </c>
-      <c r="D25" s="6">
-        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -1470,8 +1197,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="4" outlineLevelCol="3"/>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="6" outlineLevelCol="3"/>
   <cols>
     <col min="3" max="3" width="10.1" customWidth="1"/>
   </cols>
@@ -1494,13 +1221,13 @@
       <c r="A2" s="2">
         <v>460</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>5</v>
+      <c r="B2" s="3">
+        <v>11</v>
       </c>
       <c r="C2" s="4">
-        <v>8648826</v>
-      </c>
-      <c r="D2" s="5">
+        <v>9999999</v>
+      </c>
+      <c r="D2" s="4">
         <v>1024</v>
       </c>
     </row>
@@ -1508,13 +1235,13 @@
       <c r="A3" s="2">
         <v>460</v>
       </c>
-      <c r="B3" s="7" t="s">
-        <v>5</v>
+      <c r="B3" s="3">
+        <v>11</v>
       </c>
       <c r="C3" s="4">
-        <v>8648826</v>
-      </c>
-      <c r="D3" s="5">
+        <v>9999999</v>
+      </c>
+      <c r="D3" s="4">
         <v>1025</v>
       </c>
     </row>
@@ -1522,13 +1249,13 @@
       <c r="A4" s="2">
         <v>460</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>5</v>
+      <c r="B4" s="3">
+        <v>11</v>
       </c>
       <c r="C4" s="4">
-        <v>8648826</v>
-      </c>
-      <c r="D4" s="5">
+        <v>9999999</v>
+      </c>
+      <c r="D4" s="4">
         <v>1026</v>
       </c>
     </row>
@@ -1539,11 +1266,39 @@
       <c r="B5" s="3">
         <v>11</v>
       </c>
-      <c r="C5">
-        <v>7905742</v>
-      </c>
-      <c r="D5">
-        <v>2</v>
+      <c r="C5" s="4">
+        <v>8888888</v>
+      </c>
+      <c r="D5" s="4">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="2">
+        <v>460</v>
+      </c>
+      <c r="B6" s="3">
+        <v>11</v>
+      </c>
+      <c r="C6" s="4">
+        <v>8888888</v>
+      </c>
+      <c r="D6" s="4">
+        <v>1025</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="2">
+        <v>460</v>
+      </c>
+      <c r="B7" s="3">
+        <v>11</v>
+      </c>
+      <c r="C7" s="4">
+        <v>8888888</v>
+      </c>
+      <c r="D7" s="4">
+        <v>1026</v>
       </c>
     </row>
   </sheetData>

--- a/待规划小区/cell-tree-export-20250915204721.xlsx
+++ b/待规划小区/cell-tree-export-20250915204721.xlsx
@@ -56,7 +56,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="23">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -72,13 +72,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -539,152 +532,152 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -692,10 +685,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1079,8 +1071,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="6" outlineLevelCol="3"/>
+  <dimension ref="A1:D75"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="2" width="3.8" customWidth="1"/>
     <col min="3" max="3" width="9.4" customWidth="1"/>
@@ -1102,87 +1094,1039 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="5">
-        <v>460</v>
-      </c>
-      <c r="B2" s="6">
-        <v>11</v>
-      </c>
-      <c r="C2" s="4">
-        <v>999999</v>
-      </c>
-      <c r="D2" s="4">
+      <c r="A2" s="2">
+        <v>460</v>
+      </c>
+      <c r="B2" s="3">
+        <v>11</v>
+      </c>
+      <c r="C2" s="5">
+        <v>541141</v>
+      </c>
+      <c r="D2" s="5">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="2">
+        <v>460</v>
+      </c>
+      <c r="B3" s="3">
+        <v>11</v>
+      </c>
+      <c r="C3" s="5">
+        <v>541019</v>
+      </c>
+      <c r="D3" s="5">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="2">
+        <v>460</v>
+      </c>
+      <c r="B4" s="3">
+        <v>11</v>
+      </c>
+      <c r="C4" s="5">
+        <v>936260</v>
+      </c>
+      <c r="D4" s="5">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="2">
+        <v>460</v>
+      </c>
+      <c r="B5" s="3">
+        <v>11</v>
+      </c>
+      <c r="C5" s="5">
+        <v>541352</v>
+      </c>
+      <c r="D5" s="5">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="2">
+        <v>460</v>
+      </c>
+      <c r="B6" s="3">
+        <v>11</v>
+      </c>
+      <c r="C6" s="5">
+        <v>936444</v>
+      </c>
+      <c r="D6" s="5">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="2">
+        <v>460</v>
+      </c>
+      <c r="B7" s="3">
+        <v>11</v>
+      </c>
+      <c r="C7" s="5">
+        <v>936443</v>
+      </c>
+      <c r="D7" s="5">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="2">
+        <v>460</v>
+      </c>
+      <c r="B8" s="3">
+        <v>11</v>
+      </c>
+      <c r="C8" s="5">
+        <v>540906</v>
+      </c>
+      <c r="D8" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="2">
+        <v>460</v>
+      </c>
+      <c r="B9" s="3">
+        <v>11</v>
+      </c>
+      <c r="C9" s="5">
+        <v>936379</v>
+      </c>
+      <c r="D9" s="5">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="2">
+        <v>460</v>
+      </c>
+      <c r="B10" s="3">
+        <v>11</v>
+      </c>
+      <c r="C10" s="5">
+        <v>541976</v>
+      </c>
+      <c r="D10" s="5">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="2">
+        <v>460</v>
+      </c>
+      <c r="B11" s="3">
+        <v>11</v>
+      </c>
+      <c r="C11" s="5">
+        <v>542344</v>
+      </c>
+      <c r="D11" s="5">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="2">
+        <v>460</v>
+      </c>
+      <c r="B12" s="3">
+        <v>11</v>
+      </c>
+      <c r="C12" s="5">
+        <v>542248</v>
+      </c>
+      <c r="D12" s="5">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="2">
+        <v>460</v>
+      </c>
+      <c r="B13" s="3">
+        <v>11</v>
+      </c>
+      <c r="C13" s="5">
+        <v>542699</v>
+      </c>
+      <c r="D13" s="5">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="2">
+        <v>460</v>
+      </c>
+      <c r="B14" s="3">
+        <v>11</v>
+      </c>
+      <c r="C14" s="5">
+        <v>542277</v>
+      </c>
+      <c r="D14" s="5">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="2">
+        <v>460</v>
+      </c>
+      <c r="B15" s="3">
+        <v>11</v>
+      </c>
+      <c r="C15" s="5">
+        <v>541198</v>
+      </c>
+      <c r="D15" s="5">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="2">
+        <v>460</v>
+      </c>
+      <c r="B16" s="3">
+        <v>11</v>
+      </c>
+      <c r="C16" s="5">
+        <v>541650</v>
+      </c>
+      <c r="D16" s="5">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="2">
+        <v>460</v>
+      </c>
+      <c r="B17" s="3">
+        <v>11</v>
+      </c>
+      <c r="C17" s="5">
+        <v>542142</v>
+      </c>
+      <c r="D17" s="5">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="5">
-        <v>460</v>
-      </c>
-      <c r="B3" s="6">
-        <v>11</v>
-      </c>
-      <c r="C3" s="4">
-        <v>999999</v>
-      </c>
-      <c r="D3" s="4">
+    <row r="18" spans="1:4">
+      <c r="A18" s="2">
+        <v>460</v>
+      </c>
+      <c r="B18" s="3">
+        <v>11</v>
+      </c>
+      <c r="C18" s="5">
+        <v>540827</v>
+      </c>
+      <c r="D18" s="5">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="2">
+        <v>460</v>
+      </c>
+      <c r="B19" s="3">
+        <v>11</v>
+      </c>
+      <c r="C19" s="5">
+        <v>541293</v>
+      </c>
+      <c r="D19" s="5">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="2">
+        <v>460</v>
+      </c>
+      <c r="B20" s="3">
+        <v>11</v>
+      </c>
+      <c r="C20" s="5">
+        <v>541591</v>
+      </c>
+      <c r="D20" s="5">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="2">
+        <v>460</v>
+      </c>
+      <c r="B21" s="3">
+        <v>11</v>
+      </c>
+      <c r="C21" s="5">
+        <v>541053</v>
+      </c>
+      <c r="D21" s="5">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="2">
+        <v>460</v>
+      </c>
+      <c r="B22" s="3">
+        <v>11</v>
+      </c>
+      <c r="C22" s="5">
+        <v>936291</v>
+      </c>
+      <c r="D22" s="5">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="2">
+        <v>460</v>
+      </c>
+      <c r="B23" s="3">
+        <v>11</v>
+      </c>
+      <c r="C23" s="5">
+        <v>541956</v>
+      </c>
+      <c r="D23" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="2">
+        <v>460</v>
+      </c>
+      <c r="B24" s="3">
+        <v>11</v>
+      </c>
+      <c r="C24" s="5">
+        <v>540933</v>
+      </c>
+      <c r="D24" s="5">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="2">
+        <v>460</v>
+      </c>
+      <c r="B25" s="3">
+        <v>11</v>
+      </c>
+      <c r="C25" s="5">
+        <v>936380</v>
+      </c>
+      <c r="D25" s="5">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="2">
+        <v>460</v>
+      </c>
+      <c r="B26" s="3">
+        <v>11</v>
+      </c>
+      <c r="C26" s="5">
+        <v>541386</v>
+      </c>
+      <c r="D26" s="5">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="2">
+        <v>460</v>
+      </c>
+      <c r="B27" s="3">
+        <v>11</v>
+      </c>
+      <c r="C27" s="5">
+        <v>540982</v>
+      </c>
+      <c r="D27" s="5">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="2">
+        <v>460</v>
+      </c>
+      <c r="B28" s="3">
+        <v>11</v>
+      </c>
+      <c r="C28" s="5">
+        <v>541061</v>
+      </c>
+      <c r="D28" s="5">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="2">
+        <v>460</v>
+      </c>
+      <c r="B29" s="3">
+        <v>11</v>
+      </c>
+      <c r="C29" s="5">
+        <v>540890</v>
+      </c>
+      <c r="D29" s="5">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="2">
+        <v>460</v>
+      </c>
+      <c r="B30" s="3">
+        <v>11</v>
+      </c>
+      <c r="C30" s="5">
+        <v>936475</v>
+      </c>
+      <c r="D30" s="5">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="2">
+        <v>460</v>
+      </c>
+      <c r="B31" s="3">
+        <v>11</v>
+      </c>
+      <c r="C31" s="5">
+        <v>540678</v>
+      </c>
+      <c r="D31" s="5">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="2">
+        <v>460</v>
+      </c>
+      <c r="B32" s="3">
+        <v>11</v>
+      </c>
+      <c r="C32" s="5">
+        <v>540987</v>
+      </c>
+      <c r="D32" s="5">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="2">
+        <v>460</v>
+      </c>
+      <c r="B33" s="3">
+        <v>11</v>
+      </c>
+      <c r="C33" s="5">
+        <v>540964</v>
+      </c>
+      <c r="D33" s="5">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="2">
+        <v>460</v>
+      </c>
+      <c r="B34" s="3">
+        <v>11</v>
+      </c>
+      <c r="C34" s="5">
+        <v>936389</v>
+      </c>
+      <c r="D34" s="5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="2">
+        <v>460</v>
+      </c>
+      <c r="B35" s="3">
+        <v>11</v>
+      </c>
+      <c r="C35" s="5">
+        <v>540786</v>
+      </c>
+      <c r="D35" s="5">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="2">
+        <v>460</v>
+      </c>
+      <c r="B36" s="3">
+        <v>11</v>
+      </c>
+      <c r="C36" s="5">
+        <v>541400</v>
+      </c>
+      <c r="D36" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="2">
+        <v>460</v>
+      </c>
+      <c r="B37" s="3">
+        <v>11</v>
+      </c>
+      <c r="C37" s="5">
+        <v>541372</v>
+      </c>
+      <c r="D37" s="5">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="2">
+        <v>460</v>
+      </c>
+      <c r="B38" s="3">
+        <v>11</v>
+      </c>
+      <c r="C38" s="5">
+        <v>542446</v>
+      </c>
+      <c r="D38" s="5">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="2">
+        <v>460</v>
+      </c>
+      <c r="B39" s="3">
+        <v>11</v>
+      </c>
+      <c r="C39" s="5">
+        <v>541239</v>
+      </c>
+      <c r="D39" s="5">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="2">
+        <v>460</v>
+      </c>
+      <c r="B40" s="3">
+        <v>11</v>
+      </c>
+      <c r="C40" s="5">
+        <v>541115</v>
+      </c>
+      <c r="D40" s="5">
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="5">
-        <v>460</v>
-      </c>
-      <c r="B4" s="6">
-        <v>11</v>
-      </c>
-      <c r="C4" s="4">
-        <v>999999</v>
-      </c>
-      <c r="D4" s="4">
+    <row r="41" spans="1:4">
+      <c r="A41" s="2">
+        <v>460</v>
+      </c>
+      <c r="B41" s="3">
+        <v>11</v>
+      </c>
+      <c r="C41" s="5">
+        <v>936329</v>
+      </c>
+      <c r="D41" s="5">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="2">
+        <v>460</v>
+      </c>
+      <c r="B42" s="3">
+        <v>11</v>
+      </c>
+      <c r="C42" s="5">
+        <v>936327</v>
+      </c>
+      <c r="D42" s="5">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" s="2">
+        <v>460</v>
+      </c>
+      <c r="B43" s="3">
+        <v>11</v>
+      </c>
+      <c r="C43" s="5">
+        <v>542466</v>
+      </c>
+      <c r="D43" s="5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="2">
+        <v>460</v>
+      </c>
+      <c r="B44" s="3">
+        <v>11</v>
+      </c>
+      <c r="C44" s="5">
+        <v>542210</v>
+      </c>
+      <c r="D44" s="5">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" s="2">
+        <v>460</v>
+      </c>
+      <c r="B45" s="3">
+        <v>11</v>
+      </c>
+      <c r="C45" s="5">
+        <v>936389</v>
+      </c>
+      <c r="D45" s="5">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" s="2">
+        <v>460</v>
+      </c>
+      <c r="B46" s="3">
+        <v>11</v>
+      </c>
+      <c r="C46" s="5">
+        <v>541611</v>
+      </c>
+      <c r="D46" s="5">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" s="2">
+        <v>460</v>
+      </c>
+      <c r="B47" s="3">
+        <v>11</v>
+      </c>
+      <c r="C47" s="5">
+        <v>541261</v>
+      </c>
+      <c r="D47" s="5">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" s="2">
+        <v>460</v>
+      </c>
+      <c r="B48" s="3">
+        <v>11</v>
+      </c>
+      <c r="C48" s="5">
+        <v>541269</v>
+      </c>
+      <c r="D48" s="5">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" s="2">
+        <v>460</v>
+      </c>
+      <c r="B49" s="3">
+        <v>11</v>
+      </c>
+      <c r="C49" s="5">
+        <v>541087</v>
+      </c>
+      <c r="D49" s="5">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50" s="2">
+        <v>460</v>
+      </c>
+      <c r="B50" s="3">
+        <v>11</v>
+      </c>
+      <c r="C50" s="5">
+        <v>541309</v>
+      </c>
+      <c r="D50" s="5">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="5">
-        <v>460</v>
-      </c>
-      <c r="B5" s="6">
-        <v>11</v>
-      </c>
-      <c r="C5" s="4">
-        <v>888888</v>
-      </c>
-      <c r="D5" s="4">
+    <row r="51" spans="1:4">
+      <c r="A51" s="2">
+        <v>460</v>
+      </c>
+      <c r="B51" s="3">
+        <v>11</v>
+      </c>
+      <c r="C51" s="5">
+        <v>541838</v>
+      </c>
+      <c r="D51" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
+      <c r="A52" s="2">
+        <v>460</v>
+      </c>
+      <c r="B52" s="3">
+        <v>11</v>
+      </c>
+      <c r="C52" s="5">
+        <v>541361</v>
+      </c>
+      <c r="D52" s="5">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
+      <c r="A53" s="2">
+        <v>460</v>
+      </c>
+      <c r="B53" s="3">
+        <v>11</v>
+      </c>
+      <c r="C53" s="5">
+        <v>540767</v>
+      </c>
+      <c r="D53" s="5">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54" s="2">
+        <v>460</v>
+      </c>
+      <c r="B54" s="3">
+        <v>11</v>
+      </c>
+      <c r="C54" s="5">
+        <v>540905</v>
+      </c>
+      <c r="D54" s="5">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55" s="2">
+        <v>460</v>
+      </c>
+      <c r="B55" s="3">
+        <v>11</v>
+      </c>
+      <c r="C55" s="5">
+        <v>937480</v>
+      </c>
+      <c r="D55" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
+      <c r="A56" s="2">
+        <v>460</v>
+      </c>
+      <c r="B56" s="3">
+        <v>11</v>
+      </c>
+      <c r="C56" s="5">
+        <v>541027</v>
+      </c>
+      <c r="D56" s="5">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
+      <c r="A57" s="2">
+        <v>460</v>
+      </c>
+      <c r="B57" s="3">
+        <v>11</v>
+      </c>
+      <c r="C57" s="5">
+        <v>540694</v>
+      </c>
+      <c r="D57" s="5">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
+      <c r="A58" s="2">
+        <v>460</v>
+      </c>
+      <c r="B58" s="3">
+        <v>11</v>
+      </c>
+      <c r="C58" s="5">
+        <v>541399</v>
+      </c>
+      <c r="D58" s="5">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
+      <c r="A59" s="2">
+        <v>460</v>
+      </c>
+      <c r="B59" s="3">
+        <v>11</v>
+      </c>
+      <c r="C59" s="5">
+        <v>540981</v>
+      </c>
+      <c r="D59" s="5">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
+      <c r="A60" s="2">
+        <v>460</v>
+      </c>
+      <c r="B60" s="3">
+        <v>11</v>
+      </c>
+      <c r="C60" s="5">
+        <v>937485</v>
+      </c>
+      <c r="D60" s="5">
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="5">
-        <v>460</v>
-      </c>
-      <c r="B6" s="6">
-        <v>11</v>
-      </c>
-      <c r="C6" s="4">
-        <v>888888</v>
-      </c>
-      <c r="D6" s="4">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="5">
-        <v>460</v>
-      </c>
-      <c r="B7" s="6">
-        <v>11</v>
-      </c>
-      <c r="C7" s="4">
-        <v>888888</v>
-      </c>
-      <c r="D7" s="4">
+    <row r="61" spans="1:4">
+      <c r="A61" s="2">
+        <v>460</v>
+      </c>
+      <c r="B61" s="3">
+        <v>11</v>
+      </c>
+      <c r="C61" s="5">
+        <v>541273</v>
+      </c>
+      <c r="D61" s="5">
         <v>18</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
+      <c r="A62" s="2">
+        <v>460</v>
+      </c>
+      <c r="B62" s="3">
+        <v>11</v>
+      </c>
+      <c r="C62" s="5">
+        <v>542222</v>
+      </c>
+      <c r="D62" s="5">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
+      <c r="A63" s="2">
+        <v>460</v>
+      </c>
+      <c r="B63" s="3">
+        <v>11</v>
+      </c>
+      <c r="C63" s="5">
+        <v>541470</v>
+      </c>
+      <c r="D63" s="5">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
+      <c r="A64" s="2">
+        <v>460</v>
+      </c>
+      <c r="B64" s="3">
+        <v>11</v>
+      </c>
+      <c r="C64" s="5">
+        <v>541352</v>
+      </c>
+      <c r="D64" s="5">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4">
+      <c r="A65" s="2">
+        <v>460</v>
+      </c>
+      <c r="B65" s="3">
+        <v>11</v>
+      </c>
+      <c r="C65" s="5">
+        <v>937482</v>
+      </c>
+      <c r="D65" s="5">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4">
+      <c r="A66" s="2">
+        <v>460</v>
+      </c>
+      <c r="B66" s="3">
+        <v>11</v>
+      </c>
+      <c r="C66" s="5">
+        <v>542275</v>
+      </c>
+      <c r="D66" s="5">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4">
+      <c r="A67" s="2">
+        <v>460</v>
+      </c>
+      <c r="B67" s="3">
+        <v>11</v>
+      </c>
+      <c r="C67" s="5">
+        <v>540828</v>
+      </c>
+      <c r="D67" s="5">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
+      <c r="A68" s="2">
+        <v>460</v>
+      </c>
+      <c r="B68" s="3">
+        <v>11</v>
+      </c>
+      <c r="C68" s="5">
+        <v>936305</v>
+      </c>
+      <c r="D68" s="5">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4">
+      <c r="A69" s="2">
+        <v>460</v>
+      </c>
+      <c r="B69" s="3">
+        <v>11</v>
+      </c>
+      <c r="C69" s="5">
+        <v>540946</v>
+      </c>
+      <c r="D69" s="5">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4">
+      <c r="A70" s="2">
+        <v>460</v>
+      </c>
+      <c r="B70" s="3">
+        <v>11</v>
+      </c>
+      <c r="C70" s="5">
+        <v>542454</v>
+      </c>
+      <c r="D70" s="5">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4">
+      <c r="A71" s="2">
+        <v>460</v>
+      </c>
+      <c r="B71" s="3">
+        <v>11</v>
+      </c>
+      <c r="C71" s="5">
+        <v>936381</v>
+      </c>
+      <c r="D71" s="5">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4">
+      <c r="A72" s="2">
+        <v>460</v>
+      </c>
+      <c r="B72" s="3">
+        <v>11</v>
+      </c>
+      <c r="C72" s="5">
+        <v>542322</v>
+      </c>
+      <c r="D72" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4">
+      <c r="A73" s="2">
+        <v>460</v>
+      </c>
+      <c r="B73" s="3">
+        <v>11</v>
+      </c>
+      <c r="C73" s="5">
+        <v>540754</v>
+      </c>
+      <c r="D73" s="5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4">
+      <c r="A74" s="2">
+        <v>460</v>
+      </c>
+      <c r="B74" s="3">
+        <v>11</v>
+      </c>
+      <c r="C74" s="5">
+        <v>541402</v>
+      </c>
+      <c r="D74" s="5">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4">
+      <c r="A75" s="2">
+        <v>460</v>
+      </c>
+      <c r="B75" s="3">
+        <v>11</v>
+      </c>
+      <c r="C75" s="5">
+        <v>541603</v>
+      </c>
+      <c r="D75" s="5">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -1225,10 +2169,10 @@
         <v>11</v>
       </c>
       <c r="C2" s="4">
-        <v>9999999</v>
+        <v>7906317</v>
       </c>
       <c r="D2" s="4">
-        <v>1024</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1239,10 +2183,10 @@
         <v>11</v>
       </c>
       <c r="C3" s="4">
-        <v>9999999</v>
+        <v>7906317</v>
       </c>
       <c r="D3" s="4">
-        <v>1025</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1253,10 +2197,10 @@
         <v>11</v>
       </c>
       <c r="C4" s="4">
-        <v>9999999</v>
+        <v>7906317</v>
       </c>
       <c r="D4" s="4">
-        <v>1026</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1267,10 +2211,10 @@
         <v>11</v>
       </c>
       <c r="C5" s="4">
-        <v>8888888</v>
+        <v>7906620</v>
       </c>
       <c r="D5" s="4">
-        <v>1024</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1281,10 +2225,10 @@
         <v>11</v>
       </c>
       <c r="C6" s="4">
-        <v>8888888</v>
+        <v>7906620</v>
       </c>
       <c r="D6" s="4">
-        <v>1025</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1295,10 +2239,10 @@
         <v>11</v>
       </c>
       <c r="C7" s="4">
-        <v>8888888</v>
+        <v>7906620</v>
       </c>
       <c r="D7" s="4">
-        <v>1026</v>
+        <v>1600</v>
       </c>
     </row>
   </sheetData>

--- a/待规划小区/cell-tree-export-20250915204721.xlsx
+++ b/待规划小区/cell-tree-export-20250915204721.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="24685" windowHeight="11520"/>
+    <workbookView windowWidth="24685" windowHeight="11520" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="LTE" sheetId="1" r:id="rId1"/>
@@ -677,7 +677,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -685,9 +685,10 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1071,7 +1072,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:D75"/>
+  <dimension ref="A1:D47"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="2" width="3.8" customWidth="1"/>
@@ -1100,11 +1101,11 @@
       <c r="B2" s="3">
         <v>11</v>
       </c>
-      <c r="C2" s="5">
-        <v>541141</v>
-      </c>
-      <c r="D2" s="5">
-        <v>49</v>
+      <c r="C2" s="4">
+        <v>937479</v>
+      </c>
+      <c r="D2" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1114,11 +1115,11 @@
       <c r="B3" s="3">
         <v>11</v>
       </c>
-      <c r="C3" s="5">
-        <v>541019</v>
-      </c>
-      <c r="D3" s="5">
-        <v>50</v>
+      <c r="C3" s="4">
+        <v>937479</v>
+      </c>
+      <c r="D3" s="4">
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1128,11 +1129,11 @@
       <c r="B4" s="3">
         <v>11</v>
       </c>
-      <c r="C4" s="5">
-        <v>936260</v>
-      </c>
-      <c r="D4" s="5">
-        <v>24</v>
+      <c r="C4" s="4">
+        <v>937479</v>
+      </c>
+      <c r="D4" s="4">
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1142,11 +1143,11 @@
       <c r="B5" s="3">
         <v>11</v>
       </c>
-      <c r="C5" s="5">
-        <v>541352</v>
-      </c>
-      <c r="D5" s="5">
-        <v>52</v>
+      <c r="C5" s="4">
+        <v>541409</v>
+      </c>
+      <c r="D5" s="4">
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1156,11 +1157,11 @@
       <c r="B6" s="3">
         <v>11</v>
       </c>
-      <c r="C6" s="5">
-        <v>936444</v>
-      </c>
-      <c r="D6" s="5">
-        <v>53</v>
+      <c r="C6" s="4">
+        <v>541409</v>
+      </c>
+      <c r="D6" s="4">
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1170,11 +1171,11 @@
       <c r="B7" s="3">
         <v>11</v>
       </c>
-      <c r="C7" s="5">
-        <v>936443</v>
-      </c>
-      <c r="D7" s="5">
-        <v>19</v>
+      <c r="C7" s="4">
+        <v>541310</v>
+      </c>
+      <c r="D7" s="4">
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1184,949 +1185,557 @@
       <c r="B8" s="3">
         <v>11</v>
       </c>
-      <c r="C8" s="5">
-        <v>540906</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C8" s="4">
+        <v>541310</v>
+      </c>
+      <c r="D8" s="4">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="5">
+        <v>460</v>
+      </c>
+      <c r="B9" s="6">
+        <v>11</v>
+      </c>
+      <c r="C9" s="4">
+        <v>541310</v>
+      </c>
+      <c r="D9" s="4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="5">
+        <v>460</v>
+      </c>
+      <c r="B10" s="6">
+        <v>11</v>
+      </c>
+      <c r="C10" s="4">
+        <v>541419</v>
+      </c>
+      <c r="D10" s="4">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="5">
+        <v>460</v>
+      </c>
+      <c r="B11" s="6">
+        <v>11</v>
+      </c>
+      <c r="C11" s="4">
+        <v>541419</v>
+      </c>
+      <c r="D11" s="4">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="5">
+        <v>460</v>
+      </c>
+      <c r="B12" s="6">
+        <v>11</v>
+      </c>
+      <c r="C12" s="4">
+        <v>541419</v>
+      </c>
+      <c r="D12" s="4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="5">
+        <v>460</v>
+      </c>
+      <c r="B13" s="6">
+        <v>11</v>
+      </c>
+      <c r="C13" s="4">
+        <v>936502</v>
+      </c>
+      <c r="D13" s="4">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="5">
+        <v>460</v>
+      </c>
+      <c r="B14" s="6">
+        <v>11</v>
+      </c>
+      <c r="C14" s="4">
+        <v>936502</v>
+      </c>
+      <c r="D14" s="4">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="5">
+        <v>460</v>
+      </c>
+      <c r="B15" s="6">
+        <v>11</v>
+      </c>
+      <c r="C15" s="4">
+        <v>936502</v>
+      </c>
+      <c r="D15" s="4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="5">
+        <v>460</v>
+      </c>
+      <c r="B16" s="6">
+        <v>11</v>
+      </c>
+      <c r="C16" s="4">
+        <v>540709</v>
+      </c>
+      <c r="D16" s="4">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="5">
+        <v>460</v>
+      </c>
+      <c r="B17" s="6">
+        <v>11</v>
+      </c>
+      <c r="C17" s="4">
+        <v>540709</v>
+      </c>
+      <c r="D17" s="4">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="5">
+        <v>460</v>
+      </c>
+      <c r="B18" s="6">
+        <v>11</v>
+      </c>
+      <c r="C18" s="4">
+        <v>540709</v>
+      </c>
+      <c r="D18" s="4">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="5">
+        <v>460</v>
+      </c>
+      <c r="B19" s="6">
+        <v>11</v>
+      </c>
+      <c r="C19" s="4">
+        <v>540709</v>
+      </c>
+      <c r="D19" s="4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="5">
+        <v>460</v>
+      </c>
+      <c r="B20" s="6">
+        <v>11</v>
+      </c>
+      <c r="C20" s="4">
+        <v>540709</v>
+      </c>
+      <c r="D20" s="4">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="5">
+        <v>460</v>
+      </c>
+      <c r="B21" s="6">
+        <v>11</v>
+      </c>
+      <c r="C21" s="4">
+        <v>936349</v>
+      </c>
+      <c r="D21" s="4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="5">
+        <v>460</v>
+      </c>
+      <c r="B22" s="6">
+        <v>11</v>
+      </c>
+      <c r="C22" s="4">
+        <v>936349</v>
+      </c>
+      <c r="D22" s="4">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="5">
+        <v>460</v>
+      </c>
+      <c r="B23" s="6">
+        <v>11</v>
+      </c>
+      <c r="C23" s="4">
+        <v>936349</v>
+      </c>
+      <c r="D23" s="4">
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="2">
-        <v>460</v>
-      </c>
-      <c r="B9" s="3">
-        <v>11</v>
-      </c>
-      <c r="C9" s="5">
-        <v>936379</v>
-      </c>
-      <c r="D9" s="5">
+    <row r="24" spans="1:4">
+      <c r="A24" s="5">
+        <v>460</v>
+      </c>
+      <c r="B24" s="6">
+        <v>11</v>
+      </c>
+      <c r="C24" s="4">
+        <v>936349</v>
+      </c>
+      <c r="D24" s="4">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="5">
+        <v>460</v>
+      </c>
+      <c r="B25" s="6">
+        <v>11</v>
+      </c>
+      <c r="C25" s="4">
+        <v>936349</v>
+      </c>
+      <c r="D25" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="5">
+        <v>460</v>
+      </c>
+      <c r="B26" s="6">
+        <v>11</v>
+      </c>
+      <c r="C26" s="4">
+        <v>936349</v>
+      </c>
+      <c r="D26" s="4">
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="2">
-        <v>460</v>
-      </c>
-      <c r="B10" s="3">
-        <v>11</v>
-      </c>
-      <c r="C10" s="5">
-        <v>541976</v>
-      </c>
-      <c r="D10" s="5">
+    <row r="27" spans="1:4">
+      <c r="A27" s="5">
+        <v>460</v>
+      </c>
+      <c r="B27" s="6">
+        <v>11</v>
+      </c>
+      <c r="C27" s="4">
+        <v>936349</v>
+      </c>
+      <c r="D27" s="4">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="5">
+        <v>460</v>
+      </c>
+      <c r="B28" s="6">
+        <v>11</v>
+      </c>
+      <c r="C28" s="4">
+        <v>936349</v>
+      </c>
+      <c r="D28" s="4">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="5">
+        <v>460</v>
+      </c>
+      <c r="B29" s="6">
+        <v>11</v>
+      </c>
+      <c r="C29" s="4">
+        <v>936349</v>
+      </c>
+      <c r="D29" s="4">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="5">
+        <v>460</v>
+      </c>
+      <c r="B30" s="6">
+        <v>11</v>
+      </c>
+      <c r="C30" s="4">
+        <v>541394</v>
+      </c>
+      <c r="D30" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="5">
+        <v>460</v>
+      </c>
+      <c r="B31" s="6">
+        <v>11</v>
+      </c>
+      <c r="C31" s="4">
+        <v>541394</v>
+      </c>
+      <c r="D31" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="5">
+        <v>460</v>
+      </c>
+      <c r="B32" s="6">
+        <v>11</v>
+      </c>
+      <c r="C32" s="4">
+        <v>541394</v>
+      </c>
+      <c r="D32" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="5">
+        <v>460</v>
+      </c>
+      <c r="B33" s="6">
+        <v>11</v>
+      </c>
+      <c r="C33" s="4">
+        <v>540951</v>
+      </c>
+      <c r="D33" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="5">
+        <v>460</v>
+      </c>
+      <c r="B34" s="6">
+        <v>11</v>
+      </c>
+      <c r="C34" s="4">
+        <v>540951</v>
+      </c>
+      <c r="D34" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="5">
+        <v>460</v>
+      </c>
+      <c r="B35" s="6">
+        <v>11</v>
+      </c>
+      <c r="C35" s="4">
+        <v>540951</v>
+      </c>
+      <c r="D35" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="5">
+        <v>460</v>
+      </c>
+      <c r="B36" s="6">
+        <v>11</v>
+      </c>
+      <c r="C36" s="4">
+        <v>540951</v>
+      </c>
+      <c r="D36" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="5">
+        <v>460</v>
+      </c>
+      <c r="B37" s="6">
+        <v>11</v>
+      </c>
+      <c r="C37" s="4">
+        <v>540951</v>
+      </c>
+      <c r="D37" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="5">
+        <v>460</v>
+      </c>
+      <c r="B38" s="6">
+        <v>11</v>
+      </c>
+      <c r="C38" s="4">
+        <v>540951</v>
+      </c>
+      <c r="D38" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="5">
+        <v>460</v>
+      </c>
+      <c r="B39" s="6">
+        <v>11</v>
+      </c>
+      <c r="C39" s="4">
+        <v>541265</v>
+      </c>
+      <c r="D39" s="4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="5">
+        <v>460</v>
+      </c>
+      <c r="B40" s="6">
+        <v>11</v>
+      </c>
+      <c r="C40" s="4">
+        <v>541265</v>
+      </c>
+      <c r="D40" s="4">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="5">
+        <v>460</v>
+      </c>
+      <c r="B41" s="6">
+        <v>11</v>
+      </c>
+      <c r="C41" s="4">
+        <v>541265</v>
+      </c>
+      <c r="D41" s="4">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="5">
+        <v>460</v>
+      </c>
+      <c r="B42" s="6">
+        <v>11</v>
+      </c>
+      <c r="C42" s="4">
+        <v>540710</v>
+      </c>
+      <c r="D42" s="4">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" s="5">
+        <v>460</v>
+      </c>
+      <c r="B43" s="6">
+        <v>11</v>
+      </c>
+      <c r="C43" s="4">
+        <v>540710</v>
+      </c>
+      <c r="D43" s="4">
         <v>49</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="2">
-        <v>460</v>
-      </c>
-      <c r="B11" s="3">
-        <v>11</v>
-      </c>
-      <c r="C11" s="5">
-        <v>542344</v>
-      </c>
-      <c r="D11" s="5">
+    <row r="44" spans="1:4">
+      <c r="A44" s="5">
+        <v>460</v>
+      </c>
+      <c r="B44" s="6">
+        <v>11</v>
+      </c>
+      <c r="C44" s="4">
+        <v>540710</v>
+      </c>
+      <c r="D44" s="4">
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="2">
-        <v>460</v>
-      </c>
-      <c r="B12" s="3">
-        <v>11</v>
-      </c>
-      <c r="C12" s="5">
-        <v>542248</v>
-      </c>
-      <c r="D12" s="5">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="2">
-        <v>460</v>
-      </c>
-      <c r="B13" s="3">
-        <v>11</v>
-      </c>
-      <c r="C13" s="5">
-        <v>542699</v>
-      </c>
-      <c r="D13" s="5">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="2">
-        <v>460</v>
-      </c>
-      <c r="B14" s="3">
-        <v>11</v>
-      </c>
-      <c r="C14" s="5">
-        <v>542277</v>
-      </c>
-      <c r="D14" s="5">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="2">
-        <v>460</v>
-      </c>
-      <c r="B15" s="3">
-        <v>11</v>
-      </c>
-      <c r="C15" s="5">
-        <v>541198</v>
-      </c>
-      <c r="D15" s="5">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="2">
-        <v>460</v>
-      </c>
-      <c r="B16" s="3">
-        <v>11</v>
-      </c>
-      <c r="C16" s="5">
-        <v>541650</v>
-      </c>
-      <c r="D16" s="5">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="2">
-        <v>460</v>
-      </c>
-      <c r="B17" s="3">
-        <v>11</v>
-      </c>
-      <c r="C17" s="5">
-        <v>542142</v>
-      </c>
-      <c r="D17" s="5">
+    <row r="45" spans="1:4">
+      <c r="A45" s="5">
+        <v>460</v>
+      </c>
+      <c r="B45" s="6">
+        <v>11</v>
+      </c>
+      <c r="C45" s="4">
+        <v>540710</v>
+      </c>
+      <c r="D45" s="4">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="2">
-        <v>460</v>
-      </c>
-      <c r="B18" s="3">
-        <v>11</v>
-      </c>
-      <c r="C18" s="5">
-        <v>540827</v>
-      </c>
-      <c r="D18" s="5">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="2">
-        <v>460</v>
-      </c>
-      <c r="B19" s="3">
-        <v>11</v>
-      </c>
-      <c r="C19" s="5">
-        <v>541293</v>
-      </c>
-      <c r="D19" s="5">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" s="2">
-        <v>460</v>
-      </c>
-      <c r="B20" s="3">
-        <v>11</v>
-      </c>
-      <c r="C20" s="5">
-        <v>541591</v>
-      </c>
-      <c r="D20" s="5">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" s="2">
-        <v>460</v>
-      </c>
-      <c r="B21" s="3">
-        <v>11</v>
-      </c>
-      <c r="C21" s="5">
-        <v>541053</v>
-      </c>
-      <c r="D21" s="5">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" s="2">
-        <v>460</v>
-      </c>
-      <c r="B22" s="3">
-        <v>11</v>
-      </c>
-      <c r="C22" s="5">
-        <v>936291</v>
-      </c>
-      <c r="D22" s="5">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" s="2">
-        <v>460</v>
-      </c>
-      <c r="B23" s="3">
-        <v>11</v>
-      </c>
-      <c r="C23" s="5">
-        <v>541956</v>
-      </c>
-      <c r="D23" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24" s="2">
-        <v>460</v>
-      </c>
-      <c r="B24" s="3">
-        <v>11</v>
-      </c>
-      <c r="C24" s="5">
-        <v>540933</v>
-      </c>
-      <c r="D24" s="5">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" s="2">
-        <v>460</v>
-      </c>
-      <c r="B25" s="3">
-        <v>11</v>
-      </c>
-      <c r="C25" s="5">
-        <v>936380</v>
-      </c>
-      <c r="D25" s="5">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26" s="2">
-        <v>460</v>
-      </c>
-      <c r="B26" s="3">
-        <v>11</v>
-      </c>
-      <c r="C26" s="5">
-        <v>541386</v>
-      </c>
-      <c r="D26" s="5">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="A27" s="2">
-        <v>460</v>
-      </c>
-      <c r="B27" s="3">
-        <v>11</v>
-      </c>
-      <c r="C27" s="5">
-        <v>540982</v>
-      </c>
-      <c r="D27" s="5">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
-      <c r="A28" s="2">
-        <v>460</v>
-      </c>
-      <c r="B28" s="3">
-        <v>11</v>
-      </c>
-      <c r="C28" s="5">
-        <v>541061</v>
-      </c>
-      <c r="D28" s="5">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="A29" s="2">
-        <v>460</v>
-      </c>
-      <c r="B29" s="3">
-        <v>11</v>
-      </c>
-      <c r="C29" s="5">
-        <v>540890</v>
-      </c>
-      <c r="D29" s="5">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4">
-      <c r="A30" s="2">
-        <v>460</v>
-      </c>
-      <c r="B30" s="3">
-        <v>11</v>
-      </c>
-      <c r="C30" s="5">
-        <v>936475</v>
-      </c>
-      <c r="D30" s="5">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31" s="2">
-        <v>460</v>
-      </c>
-      <c r="B31" s="3">
-        <v>11</v>
-      </c>
-      <c r="C31" s="5">
-        <v>540678</v>
-      </c>
-      <c r="D31" s="5">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4">
-      <c r="A32" s="2">
-        <v>460</v>
-      </c>
-      <c r="B32" s="3">
-        <v>11</v>
-      </c>
-      <c r="C32" s="5">
-        <v>540987</v>
-      </c>
-      <c r="D32" s="5">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4">
-      <c r="A33" s="2">
-        <v>460</v>
-      </c>
-      <c r="B33" s="3">
-        <v>11</v>
-      </c>
-      <c r="C33" s="5">
-        <v>540964</v>
-      </c>
-      <c r="D33" s="5">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4">
-      <c r="A34" s="2">
-        <v>460</v>
-      </c>
-      <c r="B34" s="3">
-        <v>11</v>
-      </c>
-      <c r="C34" s="5">
-        <v>936389</v>
-      </c>
-      <c r="D34" s="5">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4">
-      <c r="A35" s="2">
-        <v>460</v>
-      </c>
-      <c r="B35" s="3">
-        <v>11</v>
-      </c>
-      <c r="C35" s="5">
-        <v>540786</v>
-      </c>
-      <c r="D35" s="5">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4">
-      <c r="A36" s="2">
-        <v>460</v>
-      </c>
-      <c r="B36" s="3">
-        <v>11</v>
-      </c>
-      <c r="C36" s="5">
-        <v>541400</v>
-      </c>
-      <c r="D36" s="5">
+    <row r="46" spans="1:4">
+      <c r="A46" s="5">
+        <v>460</v>
+      </c>
+      <c r="B46" s="6">
+        <v>11</v>
+      </c>
+      <c r="C46" s="4">
+        <v>540710</v>
+      </c>
+      <c r="D46" s="4">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" s="5">
+        <v>460</v>
+      </c>
+      <c r="B47" s="6">
+        <v>11</v>
+      </c>
+      <c r="C47" s="4">
+        <v>540710</v>
+      </c>
+      <c r="D47" s="4">
         <v>18</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4">
-      <c r="A37" s="2">
-        <v>460</v>
-      </c>
-      <c r="B37" s="3">
-        <v>11</v>
-      </c>
-      <c r="C37" s="5">
-        <v>541372</v>
-      </c>
-      <c r="D37" s="5">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4">
-      <c r="A38" s="2">
-        <v>460</v>
-      </c>
-      <c r="B38" s="3">
-        <v>11</v>
-      </c>
-      <c r="C38" s="5">
-        <v>542446</v>
-      </c>
-      <c r="D38" s="5">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4">
-      <c r="A39" s="2">
-        <v>460</v>
-      </c>
-      <c r="B39" s="3">
-        <v>11</v>
-      </c>
-      <c r="C39" s="5">
-        <v>541239</v>
-      </c>
-      <c r="D39" s="5">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4">
-      <c r="A40" s="2">
-        <v>460</v>
-      </c>
-      <c r="B40" s="3">
-        <v>11</v>
-      </c>
-      <c r="C40" s="5">
-        <v>541115</v>
-      </c>
-      <c r="D40" s="5">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4">
-      <c r="A41" s="2">
-        <v>460</v>
-      </c>
-      <c r="B41" s="3">
-        <v>11</v>
-      </c>
-      <c r="C41" s="5">
-        <v>936329</v>
-      </c>
-      <c r="D41" s="5">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4">
-      <c r="A42" s="2">
-        <v>460</v>
-      </c>
-      <c r="B42" s="3">
-        <v>11</v>
-      </c>
-      <c r="C42" s="5">
-        <v>936327</v>
-      </c>
-      <c r="D42" s="5">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4">
-      <c r="A43" s="2">
-        <v>460</v>
-      </c>
-      <c r="B43" s="3">
-        <v>11</v>
-      </c>
-      <c r="C43" s="5">
-        <v>542466</v>
-      </c>
-      <c r="D43" s="5">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4">
-      <c r="A44" s="2">
-        <v>460</v>
-      </c>
-      <c r="B44" s="3">
-        <v>11</v>
-      </c>
-      <c r="C44" s="5">
-        <v>542210</v>
-      </c>
-      <c r="D44" s="5">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4">
-      <c r="A45" s="2">
-        <v>460</v>
-      </c>
-      <c r="B45" s="3">
-        <v>11</v>
-      </c>
-      <c r="C45" s="5">
-        <v>936389</v>
-      </c>
-      <c r="D45" s="5">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4">
-      <c r="A46" s="2">
-        <v>460</v>
-      </c>
-      <c r="B46" s="3">
-        <v>11</v>
-      </c>
-      <c r="C46" s="5">
-        <v>541611</v>
-      </c>
-      <c r="D46" s="5">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4">
-      <c r="A47" s="2">
-        <v>460</v>
-      </c>
-      <c r="B47" s="3">
-        <v>11</v>
-      </c>
-      <c r="C47" s="5">
-        <v>541261</v>
-      </c>
-      <c r="D47" s="5">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4">
-      <c r="A48" s="2">
-        <v>460</v>
-      </c>
-      <c r="B48" s="3">
-        <v>11</v>
-      </c>
-      <c r="C48" s="5">
-        <v>541269</v>
-      </c>
-      <c r="D48" s="5">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4">
-      <c r="A49" s="2">
-        <v>460</v>
-      </c>
-      <c r="B49" s="3">
-        <v>11</v>
-      </c>
-      <c r="C49" s="5">
-        <v>541087</v>
-      </c>
-      <c r="D49" s="5">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4">
-      <c r="A50" s="2">
-        <v>460</v>
-      </c>
-      <c r="B50" s="3">
-        <v>11</v>
-      </c>
-      <c r="C50" s="5">
-        <v>541309</v>
-      </c>
-      <c r="D50" s="5">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4">
-      <c r="A51" s="2">
-        <v>460</v>
-      </c>
-      <c r="B51" s="3">
-        <v>11</v>
-      </c>
-      <c r="C51" s="5">
-        <v>541838</v>
-      </c>
-      <c r="D51" s="5">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4">
-      <c r="A52" s="2">
-        <v>460</v>
-      </c>
-      <c r="B52" s="3">
-        <v>11</v>
-      </c>
-      <c r="C52" s="5">
-        <v>541361</v>
-      </c>
-      <c r="D52" s="5">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4">
-      <c r="A53" s="2">
-        <v>460</v>
-      </c>
-      <c r="B53" s="3">
-        <v>11</v>
-      </c>
-      <c r="C53" s="5">
-        <v>540767</v>
-      </c>
-      <c r="D53" s="5">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4">
-      <c r="A54" s="2">
-        <v>460</v>
-      </c>
-      <c r="B54" s="3">
-        <v>11</v>
-      </c>
-      <c r="C54" s="5">
-        <v>540905</v>
-      </c>
-      <c r="D54" s="5">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4">
-      <c r="A55" s="2">
-        <v>460</v>
-      </c>
-      <c r="B55" s="3">
-        <v>11</v>
-      </c>
-      <c r="C55" s="5">
-        <v>937480</v>
-      </c>
-      <c r="D55" s="5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4">
-      <c r="A56" s="2">
-        <v>460</v>
-      </c>
-      <c r="B56" s="3">
-        <v>11</v>
-      </c>
-      <c r="C56" s="5">
-        <v>541027</v>
-      </c>
-      <c r="D56" s="5">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4">
-      <c r="A57" s="2">
-        <v>460</v>
-      </c>
-      <c r="B57" s="3">
-        <v>11</v>
-      </c>
-      <c r="C57" s="5">
-        <v>540694</v>
-      </c>
-      <c r="D57" s="5">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4">
-      <c r="A58" s="2">
-        <v>460</v>
-      </c>
-      <c r="B58" s="3">
-        <v>11</v>
-      </c>
-      <c r="C58" s="5">
-        <v>541399</v>
-      </c>
-      <c r="D58" s="5">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4">
-      <c r="A59" s="2">
-        <v>460</v>
-      </c>
-      <c r="B59" s="3">
-        <v>11</v>
-      </c>
-      <c r="C59" s="5">
-        <v>540981</v>
-      </c>
-      <c r="D59" s="5">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4">
-      <c r="A60" s="2">
-        <v>460</v>
-      </c>
-      <c r="B60" s="3">
-        <v>11</v>
-      </c>
-      <c r="C60" s="5">
-        <v>937485</v>
-      </c>
-      <c r="D60" s="5">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4">
-      <c r="A61" s="2">
-        <v>460</v>
-      </c>
-      <c r="B61" s="3">
-        <v>11</v>
-      </c>
-      <c r="C61" s="5">
-        <v>541273</v>
-      </c>
-      <c r="D61" s="5">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4">
-      <c r="A62" s="2">
-        <v>460</v>
-      </c>
-      <c r="B62" s="3">
-        <v>11</v>
-      </c>
-      <c r="C62" s="5">
-        <v>542222</v>
-      </c>
-      <c r="D62" s="5">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4">
-      <c r="A63" s="2">
-        <v>460</v>
-      </c>
-      <c r="B63" s="3">
-        <v>11</v>
-      </c>
-      <c r="C63" s="5">
-        <v>541470</v>
-      </c>
-      <c r="D63" s="5">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4">
-      <c r="A64" s="2">
-        <v>460</v>
-      </c>
-      <c r="B64" s="3">
-        <v>11</v>
-      </c>
-      <c r="C64" s="5">
-        <v>541352</v>
-      </c>
-      <c r="D64" s="5">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4">
-      <c r="A65" s="2">
-        <v>460</v>
-      </c>
-      <c r="B65" s="3">
-        <v>11</v>
-      </c>
-      <c r="C65" s="5">
-        <v>937482</v>
-      </c>
-      <c r="D65" s="5">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4">
-      <c r="A66" s="2">
-        <v>460</v>
-      </c>
-      <c r="B66" s="3">
-        <v>11</v>
-      </c>
-      <c r="C66" s="5">
-        <v>542275</v>
-      </c>
-      <c r="D66" s="5">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4">
-      <c r="A67" s="2">
-        <v>460</v>
-      </c>
-      <c r="B67" s="3">
-        <v>11</v>
-      </c>
-      <c r="C67" s="5">
-        <v>540828</v>
-      </c>
-      <c r="D67" s="5">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4">
-      <c r="A68" s="2">
-        <v>460</v>
-      </c>
-      <c r="B68" s="3">
-        <v>11</v>
-      </c>
-      <c r="C68" s="5">
-        <v>936305</v>
-      </c>
-      <c r="D68" s="5">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4">
-      <c r="A69" s="2">
-        <v>460</v>
-      </c>
-      <c r="B69" s="3">
-        <v>11</v>
-      </c>
-      <c r="C69" s="5">
-        <v>540946</v>
-      </c>
-      <c r="D69" s="5">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4">
-      <c r="A70" s="2">
-        <v>460</v>
-      </c>
-      <c r="B70" s="3">
-        <v>11</v>
-      </c>
-      <c r="C70" s="5">
-        <v>542454</v>
-      </c>
-      <c r="D70" s="5">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4">
-      <c r="A71" s="2">
-        <v>460</v>
-      </c>
-      <c r="B71" s="3">
-        <v>11</v>
-      </c>
-      <c r="C71" s="5">
-        <v>936381</v>
-      </c>
-      <c r="D71" s="5">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4">
-      <c r="A72" s="2">
-        <v>460</v>
-      </c>
-      <c r="B72" s="3">
-        <v>11</v>
-      </c>
-      <c r="C72" s="5">
-        <v>542322</v>
-      </c>
-      <c r="D72" s="5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4">
-      <c r="A73" s="2">
-        <v>460</v>
-      </c>
-      <c r="B73" s="3">
-        <v>11</v>
-      </c>
-      <c r="C73" s="5">
-        <v>540754</v>
-      </c>
-      <c r="D73" s="5">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4">
-      <c r="A74" s="2">
-        <v>460</v>
-      </c>
-      <c r="B74" s="3">
-        <v>11</v>
-      </c>
-      <c r="C74" s="5">
-        <v>541402</v>
-      </c>
-      <c r="D74" s="5">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4">
-      <c r="A75" s="2">
-        <v>460</v>
-      </c>
-      <c r="B75" s="3">
-        <v>11</v>
-      </c>
-      <c r="C75" s="5">
-        <v>541603</v>
-      </c>
-      <c r="D75" s="5">
-        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -2141,8 +1750,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="6" outlineLevelCol="3"/>
+  <dimension ref="A1:D42"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="3"/>
   <cols>
     <col min="3" max="3" width="10.1" customWidth="1"/>
   </cols>
@@ -2169,10 +1778,10 @@
         <v>11</v>
       </c>
       <c r="C2" s="4">
-        <v>7906317</v>
+        <v>7905741</v>
       </c>
       <c r="D2" s="4">
-        <v>1604</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -2183,10 +1792,10 @@
         <v>11</v>
       </c>
       <c r="C3" s="4">
-        <v>7906317</v>
+        <v>7905741</v>
       </c>
       <c r="D3" s="4">
-        <v>1605</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -2197,10 +1806,10 @@
         <v>11</v>
       </c>
       <c r="C4" s="4">
-        <v>7906317</v>
+        <v>7905741</v>
       </c>
       <c r="D4" s="4">
-        <v>1603</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2211,10 +1820,10 @@
         <v>11</v>
       </c>
       <c r="C5" s="4">
-        <v>7906620</v>
+        <v>7905734</v>
       </c>
       <c r="D5" s="4">
-        <v>1601</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2225,24 +1834,514 @@
         <v>11</v>
       </c>
       <c r="C6" s="4">
-        <v>7906620</v>
+        <v>7905734</v>
       </c>
       <c r="D6" s="4">
-        <v>1602</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="2">
-        <v>460</v>
-      </c>
-      <c r="B7" s="3">
+      <c r="A7" s="5">
+        <v>460</v>
+      </c>
+      <c r="B7" s="6">
         <v>11</v>
       </c>
       <c r="C7" s="4">
-        <v>7906620</v>
+        <v>7905734</v>
       </c>
       <c r="D7" s="4">
-        <v>1600</v>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="5">
+        <v>460</v>
+      </c>
+      <c r="B8" s="6">
+        <v>11</v>
+      </c>
+      <c r="C8" s="4">
+        <v>7905707</v>
+      </c>
+      <c r="D8" s="4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="5">
+        <v>460</v>
+      </c>
+      <c r="B9" s="6">
+        <v>11</v>
+      </c>
+      <c r="C9" s="4">
+        <v>7905707</v>
+      </c>
+      <c r="D9" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="5">
+        <v>460</v>
+      </c>
+      <c r="B10" s="6">
+        <v>11</v>
+      </c>
+      <c r="C10" s="4">
+        <v>7905707</v>
+      </c>
+      <c r="D10" s="4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="5">
+        <v>460</v>
+      </c>
+      <c r="B11" s="6">
+        <v>11</v>
+      </c>
+      <c r="C11" s="4">
+        <v>7905651</v>
+      </c>
+      <c r="D11" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="5">
+        <v>460</v>
+      </c>
+      <c r="B12" s="6">
+        <v>11</v>
+      </c>
+      <c r="C12" s="4">
+        <v>7905651</v>
+      </c>
+      <c r="D12" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="5">
+        <v>460</v>
+      </c>
+      <c r="B13" s="6">
+        <v>11</v>
+      </c>
+      <c r="C13" s="4">
+        <v>7905651</v>
+      </c>
+      <c r="D13" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="5">
+        <v>460</v>
+      </c>
+      <c r="B14" s="6">
+        <v>11</v>
+      </c>
+      <c r="C14" s="4">
+        <v>7906410</v>
+      </c>
+      <c r="D14" s="4">
+        <v>1609</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="5">
+        <v>460</v>
+      </c>
+      <c r="B15" s="6">
+        <v>11</v>
+      </c>
+      <c r="C15" s="4">
+        <v>7906410</v>
+      </c>
+      <c r="D15" s="4">
+        <v>1610</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="5">
+        <v>460</v>
+      </c>
+      <c r="B16" s="6">
+        <v>11</v>
+      </c>
+      <c r="C16" s="4">
+        <v>7906410</v>
+      </c>
+      <c r="D16" s="4">
+        <v>1611</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="5">
+        <v>460</v>
+      </c>
+      <c r="B17" s="6">
+        <v>11</v>
+      </c>
+      <c r="C17" s="4">
+        <v>7906376</v>
+      </c>
+      <c r="D17" s="4">
+        <v>1603</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="5">
+        <v>460</v>
+      </c>
+      <c r="B18" s="6">
+        <v>11</v>
+      </c>
+      <c r="C18" s="4">
+        <v>7906376</v>
+      </c>
+      <c r="D18" s="4">
+        <v>1604</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="5">
+        <v>460</v>
+      </c>
+      <c r="B19" s="6">
+        <v>11</v>
+      </c>
+      <c r="C19" s="4">
+        <v>7906376</v>
+      </c>
+      <c r="D19" s="4">
+        <v>1605</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="5">
+        <v>460</v>
+      </c>
+      <c r="B20" s="6">
+        <v>11</v>
+      </c>
+      <c r="C20" s="4">
+        <v>7905802</v>
+      </c>
+      <c r="D20" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="5">
+        <v>460</v>
+      </c>
+      <c r="B21" s="6">
+        <v>11</v>
+      </c>
+      <c r="C21" s="4">
+        <v>7905802</v>
+      </c>
+      <c r="D21" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="5">
+        <v>460</v>
+      </c>
+      <c r="B22" s="6">
+        <v>11</v>
+      </c>
+      <c r="C22" s="4">
+        <v>7905802</v>
+      </c>
+      <c r="D22" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="5">
+        <v>460</v>
+      </c>
+      <c r="B23" s="6">
+        <v>11</v>
+      </c>
+      <c r="C23" s="4">
+        <v>7905813</v>
+      </c>
+      <c r="D23" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="5">
+        <v>460</v>
+      </c>
+      <c r="B24" s="6">
+        <v>11</v>
+      </c>
+      <c r="C24" s="4">
+        <v>7905813</v>
+      </c>
+      <c r="D24" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="5">
+        <v>460</v>
+      </c>
+      <c r="B25" s="6">
+        <v>11</v>
+      </c>
+      <c r="C25" s="4">
+        <v>7905813</v>
+      </c>
+      <c r="D25" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="5">
+        <v>460</v>
+      </c>
+      <c r="B26" s="6">
+        <v>11</v>
+      </c>
+      <c r="C26" s="4">
+        <v>7905867</v>
+      </c>
+      <c r="D26" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="5">
+        <v>460</v>
+      </c>
+      <c r="B27" s="6">
+        <v>11</v>
+      </c>
+      <c r="C27" s="4">
+        <v>7905867</v>
+      </c>
+      <c r="D27" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="5">
+        <v>460</v>
+      </c>
+      <c r="B28" s="6">
+        <v>11</v>
+      </c>
+      <c r="C28" s="4">
+        <v>7905867</v>
+      </c>
+      <c r="D28" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="5">
+        <v>460</v>
+      </c>
+      <c r="B29" s="6">
+        <v>11</v>
+      </c>
+      <c r="C29" s="4">
+        <v>7905865</v>
+      </c>
+      <c r="D29" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="5">
+        <v>460</v>
+      </c>
+      <c r="B30" s="6">
+        <v>11</v>
+      </c>
+      <c r="C30" s="4">
+        <v>7905865</v>
+      </c>
+      <c r="D30" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="5">
+        <v>460</v>
+      </c>
+      <c r="B31" s="6">
+        <v>11</v>
+      </c>
+      <c r="C31" s="4">
+        <v>7905346</v>
+      </c>
+      <c r="D31" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="5">
+        <v>460</v>
+      </c>
+      <c r="B32" s="6">
+        <v>11</v>
+      </c>
+      <c r="C32" s="4">
+        <v>7905346</v>
+      </c>
+      <c r="D32" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="5">
+        <v>460</v>
+      </c>
+      <c r="B33" s="6">
+        <v>11</v>
+      </c>
+      <c r="C33" s="4">
+        <v>7905346</v>
+      </c>
+      <c r="D33" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="5">
+        <v>460</v>
+      </c>
+      <c r="B34" s="6">
+        <v>11</v>
+      </c>
+      <c r="C34" s="4">
+        <v>7905443</v>
+      </c>
+      <c r="D34" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="5">
+        <v>460</v>
+      </c>
+      <c r="B35" s="6">
+        <v>11</v>
+      </c>
+      <c r="C35" s="4">
+        <v>7905443</v>
+      </c>
+      <c r="D35" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="5">
+        <v>460</v>
+      </c>
+      <c r="B36" s="6">
+        <v>11</v>
+      </c>
+      <c r="C36" s="4">
+        <v>7905443</v>
+      </c>
+      <c r="D36" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="5">
+        <v>460</v>
+      </c>
+      <c r="B37" s="6">
+        <v>11</v>
+      </c>
+      <c r="C37" s="4">
+        <v>7905315</v>
+      </c>
+      <c r="D37" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="5">
+        <v>460</v>
+      </c>
+      <c r="B38" s="6">
+        <v>11</v>
+      </c>
+      <c r="C38" s="4">
+        <v>7905315</v>
+      </c>
+      <c r="D38" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="5">
+        <v>460</v>
+      </c>
+      <c r="B39" s="6">
+        <v>11</v>
+      </c>
+      <c r="C39" s="4">
+        <v>7905315</v>
+      </c>
+      <c r="D39" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="5">
+        <v>460</v>
+      </c>
+      <c r="B40" s="6">
+        <v>11</v>
+      </c>
+      <c r="C40" s="4">
+        <v>7905317</v>
+      </c>
+      <c r="D40" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="5">
+        <v>460</v>
+      </c>
+      <c r="B41" s="6">
+        <v>11</v>
+      </c>
+      <c r="C41" s="4">
+        <v>7905317</v>
+      </c>
+      <c r="D41" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="5">
+        <v>460</v>
+      </c>
+      <c r="B42" s="6">
+        <v>11</v>
+      </c>
+      <c r="C42" s="4">
+        <v>7905317</v>
+      </c>
+      <c r="D42" s="4">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
